--- a/backend/templates/Cash Request.xlsx
+++ b/backend/templates/Cash Request.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jajrc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\procurement\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA196D-BEB5-4665-A417-07461F8624A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA069EC-385A-4CBF-AC04-23C765BFF102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CA967CE1-F0DD-4DCC-BBE1-A47F59AE10B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{CA967CE1-F0DD-4DCC-BBE1-A47F59AE10B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>JAJr CONSTRUCTION</t>
   </si>
@@ -50,18 +50,6 @@
     <t>E-mail Address: jajrconstruction@yahoo.com</t>
   </si>
   <si>
-    <t xml:space="preserve">CASH REQUEST </t>
-  </si>
-  <si>
-    <t>PR# : Dept- Year-Month-Seq. No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECEIVER: </t>
-  </si>
-  <si>
     <t xml:space="preserve">Date Prepared: </t>
   </si>
   <si>
@@ -101,25 +89,31 @@
     <t>Reviewed by:</t>
   </si>
   <si>
-    <t xml:space="preserve">Approved by: </t>
-  </si>
-  <si>
-    <t>JUNELL B. TADINA</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARC JUSTIN E. ARZADON </t>
   </si>
   <si>
-    <t xml:space="preserve">Planning Engineer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procurement Officer </t>
-  </si>
-  <si>
     <t xml:space="preserve">General Manager </t>
   </si>
   <si>
-    <t>Order Number:</t>
+    <t>PR# : Initials- Year-Month-Seq. No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPLIER : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received by: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name and Signature </t>
+  </si>
+  <si>
+    <t>Name and Signature</t>
+  </si>
+  <si>
+    <t>Reviewed by;</t>
+  </si>
+  <si>
+    <t>PETTY CASH REQUEST</t>
   </si>
 </sst>
 </file>
@@ -127,7 +121,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -154,12 +148,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -234,6 +222,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -243,7 +238,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -560,17 +555,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -629,6 +613,30 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -638,10 +646,109 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -669,299 +776,188 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1026,6 +1022,128 @@
         <a:xfrm>
           <a:off x="273118" y="92449"/>
           <a:ext cx="1012757" cy="866775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>377893</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>92449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>113791</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>149599</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC72BF99-EEF9-4CDB-98D3-A186F063977D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="377893" y="92449"/>
+          <a:ext cx="1193223" cy="781050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>277040</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>103655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>201706</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>160805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95FAB849-92F7-4BC8-A202-30B02A0E1478}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="277040" y="103655"/>
+          <a:ext cx="1381991" cy="781050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1364,456 +1482,425 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF167A1-C557-4F70-87B1-8A5AB75ABC80}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="32.42578125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="44"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="57"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="48"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="58"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="59"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="28" t="s">
+      <c r="B10" s="69"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="105"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="B11" s="71"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="74"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="C12" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="110" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="111"/>
-      <c r="E10" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="112"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="D12" s="76"/>
+      <c r="E12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-    </row>
-    <row r="13" spans="1:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48" t="s">
+      <c r="F12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="49" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="23"/>
+    </row>
+    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="96"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="93"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="97"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="48" t="s">
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="E31" s="99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="100"/>
+    </row>
+    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="101"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="61"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="64"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="63"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="63"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="64"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="63"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="59"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="63"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="64"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="63"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="70"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="75" t="s">
+      <c r="F32" s="104"/>
+    </row>
+    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="104"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78">
-        <f>SUM(F13:F29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="79"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="84" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="86"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="87"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="89" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="89" t="s">
+      <c r="F34" s="84"/>
+    </row>
+    <row r="35" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="31"/>
+    </row>
+    <row r="36" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="34"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31"/>
+    </row>
+    <row r="37" spans="1:6" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="85"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="31"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="90"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="91"/>
-      <c r="B34" s="88"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="90"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="94" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="95" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="96"/>
-    </row>
-    <row r="36" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A36" s="97"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="99"/>
-    </row>
-    <row r="37" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="100"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="102"/>
-    </row>
-    <row r="38" spans="1:6" ht="26.25" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="103"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="102"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="105"/>
-      <c r="B39" s="106"/>
-      <c r="C39" s="106"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
-    </row>
-    <row r="40" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="107"/>
-      <c r="B40" s="108"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="108"/>
-      <c r="F40" s="109"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="31"/>
+    </row>
+    <row r="39" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="30"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="E35:F35"/>
+  <mergeCells count="51">
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:F33"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="C11:F12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
@@ -1821,6 +1908,14 @@
     <mergeCell ref="A5:D7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
